--- a/00. Document/03. 개발문서/든든하이_API명세서(25-0508).xlsx
+++ b/00. Document/03. 개발문서/든든하이_API명세서(25-0508).xlsx
@@ -1,44 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dkfks\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\2025_Project\00. Document\03. 개발문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EBB16C-437B-4743-8C16-CE7382BCF3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89506AA5-7A0E-464D-9749-B64B4D3F70E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="API 목록" sheetId="1" r:id="rId1"/>
-    <sheet name="사용자 등록" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="패스워드 찾기" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="signupf" sheetId="5" r:id="rId4"/>
-    <sheet name="폴더 생성" sheetId="131" state="hidden" r:id="rId5"/>
-    <sheet name="폴더 삭제" sheetId="132" state="hidden" r:id="rId6"/>
+    <sheet name="Weather" sheetId="134" r:id="rId2"/>
+    <sheet name="signupf" sheetId="5" r:id="rId3"/>
+    <sheet name="사용자 등록" sheetId="2" state="hidden" r:id="rId4"/>
+    <sheet name="패스워드 찾기" sheetId="3" state="hidden" r:id="rId5"/>
+    <sheet name="폴더 생성" sheetId="131" state="hidden" r:id="rId6"/>
+    <sheet name="폴더 삭제" sheetId="132" state="hidden" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="144">
   <si>
     <t>URL prefix</t>
   </si>
@@ -317,20 +305,288 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>API 명</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>API 주소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>메소드 타입</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">- 각 API 별 상세 명세는 하단 시트로 추가 부탁드립니다.
 - 메소드 타입은 GET, POST, PUT, DELETE, OPTION . . . </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>인증키</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>serviceKey</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>공공데이터포털에서 발급받은 인증키</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>numOfRows</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 페이지 결과 수정</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>페이지 번호</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>pageNo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>응답자료형식</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>발표일자</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>발표시각</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>예보지점 X 좌표</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>예보지점 Y 좌표</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>nx</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ny</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>base_time</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>base_date</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>요청자료형식(XML/JSON)
+Default: XML</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>06시 발표(정시단위)
+-매시각 10분 이후 호출</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>예보지점의 X 좌표값</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>예보지점의 Y 좌표값</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>유저 회원 계정</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>페이지 번호
+Default: 1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>‘25년 5월 1일 발표'
+- 조회할 일자 호출</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>변수명</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>key</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>totalCount</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>resultCode</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>resultMsg</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseDate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseTime</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>category</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 총 개수</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>응답메세지 코드</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>응답메세지 내용</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 페이지 결과 수</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 타입</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>자료구분코드</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>페이지 수</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>응답 메시지코드</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>응답 메시지 설명</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>응답자료형식(XML/JSON)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>06시 발표(매 정시)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력한 예보지점 X 좌표</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력한 예보지점 Y 좌표</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 페이지당 표출
+데이터 수</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apis.data.go.kr/1360000/VilageFcstInfoService_2.0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>weather</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>GET</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>예보일자</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>예보시각</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>fcstDate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>fcstTime</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>예보값</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>fcstValue</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>자료구분문자</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">기상청 날씨 연동 - 사용자용 날씨 제공 API 시스템
+앱 사용자에게 날씨 정보를 제공하기 위해, 서버에서 기상청 데이터를 가져와 사용자 요청에 응답하는 API를 제공합니다. 이 API는 주기적으로 기상청 데이터를 갱신하며, 사용자 위치 기반의 날씨 정보를 제공합니다.
+1) Client(App) → WeatherServer
+    API 요청    
+2) WeatherServer → 기상청 OpenAPI
+    WeatherServer는 내부적으로 기상청 OpenAPI를 호출하여 날씨 데이터 응답
+3) WeatherServer → Client(App)
+   응답받은 날씨 정보는 앱 내 사용자 화면에 표시
+   응답 성공시 응답받는 데이터를 User DB에 등록 
+4) 특별한 상황에 실패값 응답 및 기타 응답 실패시 
+    기상청 응답 실패 시, 서버 내부에 캐싱된 데이터를 제공
+    캐시도 없는 경우 "status": "error" 와 함께 에러 메시지 반환
+    일반적인 정상 상황은 최신 날씨 데이터를 리턴하며 성공을 반환합니다.
+5) AccountId, 닉네임 생성 관련 일반 정형화된 기본 방식 (Null Or WhiteSpace, 특수문자 금지등)
+    사용하여 구현 부탁 드립니다.
+    다만 길이 관련해서는 싱크가 필요해서
+    AccountId, Nickname 두 부분은 2자 이상 ~ 16자리 이하
+</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>‘25년 5월 1일 예보'</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>조회할 일자 호출
+20250501 - ‘25년 5월 1일 발표'</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0500 - 05시 발표</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>자료는 실수 또는 정수로 제공
+- TMP, TMN, TMX, UUU, VVV, WAV, WSD</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>int/float</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -946,7 +1202,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1105,6 +1361,31 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1132,6 +1413,120 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1141,6 +1536,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1162,135 +1572,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1306,6 +1587,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
@@ -1613,59 +1895,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.375" customWidth="1"/>
+    <col min="2" max="2" width="33.3984375" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="11" customWidth="1"/>
-    <col min="4" max="4" width="19.125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="19.09765625" style="11" customWidth="1"/>
     <col min="5" max="5" width="24.5" customWidth="1"/>
     <col min="12" max="12" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-    </row>
-    <row r="2" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.6"/>
-    <row r="3" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="55" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+    </row>
+    <row r="2" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="57"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="66"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="60"/>
-    </row>
-    <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="69"/>
+    </row>
+    <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="60"/>
-    </row>
-    <row r="6" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65"/>
-    <row r="7" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="69"/>
+    </row>
+    <row r="6" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="29" t="s">
         <v>3</v>
       </c>
@@ -1681,15 +1963,15 @@
       <c r="E7" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="61" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
-    </row>
-    <row r="8" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G7" s="70" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20" t="s">
         <v>74</v>
       </c>
@@ -1704,323 +1986,325 @@
       </c>
       <c r="E8" s="37"/>
       <c r="F8" s="33"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-    </row>
-    <row r="9" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>80</v>
+        <v>129</v>
+      </c>
+      <c r="B9" s="62" t="s">
+        <v>128</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="21"/>
+        <v>130</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="E9" s="37"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="62"/>
-    </row>
-    <row r="10" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+    </row>
+    <row r="10" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20"/>
       <c r="B10" s="31"/>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
       <c r="E10" s="37"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
-    </row>
-    <row r="11" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="71"/>
+    </row>
+    <row r="11" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="27"/>
       <c r="B11" s="31"/>
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
       <c r="E11" s="38"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="62"/>
-    </row>
-    <row r="12" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+    </row>
+    <row r="12" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="31"/>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="39"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="62"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="71"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="20"/>
       <c r="B13" s="31"/>
       <c r="C13" s="21"/>
       <c r="D13" s="21"/>
       <c r="E13" s="37"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
-    </row>
-    <row r="14" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+    </row>
+    <row r="14" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="23"/>
       <c r="B14" s="31"/>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
       <c r="E14" s="37"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="20"/>
       <c r="B15" s="31"/>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
       <c r="E15" s="40"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="62"/>
-    </row>
-    <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+    </row>
+    <row r="16" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="23"/>
       <c r="B16" s="31"/>
       <c r="C16" s="21"/>
       <c r="D16" s="21"/>
       <c r="E16" s="41"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="62"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="20"/>
       <c r="B17" s="31"/>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
       <c r="E17" s="37"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="22"/>
       <c r="B18" s="31"/>
       <c r="C18" s="21"/>
       <c r="D18" s="21"/>
       <c r="E18" s="42"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="71"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="27"/>
       <c r="B19" s="31"/>
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
       <c r="E19" s="38"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-    </row>
-    <row r="20" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+    </row>
+    <row r="20" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
       <c r="B20" s="31"/>
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
       <c r="E20" s="43"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="71"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="20"/>
       <c r="B21" s="31"/>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
       <c r="E21" s="44"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="71"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="20"/>
       <c r="B22" s="31"/>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="37"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="34"/>
       <c r="B23" s="36"/>
       <c r="C23" s="35"/>
       <c r="D23" s="35"/>
       <c r="E23" s="37"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="71"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="34"/>
       <c r="B24" s="36"/>
       <c r="C24" s="35"/>
       <c r="D24" s="35"/>
       <c r="E24" s="37"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="34"/>
       <c r="B25" s="36"/>
       <c r="C25" s="35"/>
       <c r="D25" s="35"/>
       <c r="E25" s="37"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="34"/>
       <c r="B26" s="36"/>
       <c r="C26" s="35"/>
       <c r="D26" s="35"/>
       <c r="E26" s="37"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="71"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="34"/>
       <c r="B27" s="36"/>
       <c r="C27" s="35"/>
       <c r="D27" s="35"/>
       <c r="E27" s="37"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="20"/>
       <c r="B28" s="31"/>
       <c r="C28" s="24"/>
       <c r="D28" s="21"/>
       <c r="E28" s="37"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="71"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="22"/>
       <c r="B29" s="45"/>
       <c r="C29" s="24"/>
       <c r="D29" s="28"/>
       <c r="E29" s="42"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="27"/>
       <c r="B30" s="45"/>
       <c r="C30" s="24"/>
       <c r="D30" s="28"/>
       <c r="E30" s="38"/>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62"/>
-    </row>
-    <row r="31" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
+    </row>
+    <row r="31" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="25"/>
       <c r="B31" s="46"/>
       <c r="C31" s="24"/>
       <c r="D31" s="26"/>
       <c r="E31" s="43"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="62"/>
-      <c r="K31" s="62"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.6">
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="71"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="20"/>
       <c r="B32" s="47"/>
       <c r="C32" s="24"/>
       <c r="D32" s="21"/>
       <c r="E32" s="44"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="71"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" s="34"/>
       <c r="B33" s="48"/>
       <c r="C33" s="35"/>
       <c r="D33" s="35"/>
       <c r="E33" s="37"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" s="34"/>
       <c r="B34" s="48"/>
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
       <c r="E34" s="37"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="D37" s="49"/>
     </row>
   </sheetData>
@@ -2035,405 +2319,144 @@
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" xr:uid="{26A66FDA-DE9D-4CDA-8C08-F5E0844A3521}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{E94C07D4-A7B8-4155-BE3E-28FCD3AACD94}"/>
+    <hyperlink ref="B9" r:id="rId3" xr:uid="{FADB24DC-83D9-4E9C-8870-3900002B6341}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B01C7F2-82BF-43ED-9E3F-E35294B1DBC5}">
+  <dimension ref="A1:S39"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.5" customWidth="1"/>
-    <col min="3" max="3" width="9.875" customWidth="1"/>
-    <col min="5" max="5" width="33.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="65"/>
-    </row>
-    <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A4" s="66" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="70" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="70"/>
-      <c r="E5" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A8" s="66" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="71" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="72"/>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A10" s="71" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="68" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="E13" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-  </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="E13" location="'API 목록'!A1" display="API 목록 가기" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
-  <cols>
-    <col min="1" max="1" width="7.5" customWidth="1"/>
-    <col min="3" max="3" width="9.875" customWidth="1"/>
-    <col min="5" max="5" width="33.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="63" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="65"/>
-    </row>
-    <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A4" s="66" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="70" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="70"/>
-      <c r="E5" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A8" s="66" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="71" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="72"/>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="A10" s="71" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="68" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="E13" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-  </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="E13" location="'API 목록'!A1" display="API 목록 가기" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:S28"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
-  <cols>
-    <col min="1" max="1" width="6.25" customWidth="1"/>
-    <col min="2" max="2" width="13.625" customWidth="1"/>
-    <col min="3" max="5" width="2.875" customWidth="1"/>
-    <col min="6" max="6" width="9.125" customWidth="1"/>
-    <col min="7" max="7" width="44.25" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="11" customWidth="1"/>
+    <col min="1" max="1" width="6.19921875" customWidth="1"/>
+    <col min="2" max="2" width="13.59765625" customWidth="1"/>
+    <col min="3" max="5" width="2.8984375" customWidth="1"/>
+    <col min="6" max="6" width="9.09765625" customWidth="1"/>
+    <col min="7" max="7" width="44.19921875" customWidth="1"/>
+    <col min="8" max="8" width="9.19921875" style="11" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="63" t="str">
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="110" t="str">
         <f>'API 목록'!A8</f>
         <v>signupf</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="65"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.6">
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="112"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="82" t="s">
+      <c r="K3" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="82" t="s">
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="83"/>
-      <c r="S3" s="84"/>
-    </row>
-    <row r="4" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="81" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="100"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="102"/>
-      <c r="S4" s="103"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.6">
-      <c r="K5" s="107"/>
-      <c r="L5" s="108"/>
-      <c r="M5" s="108"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="109"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="111"/>
-      <c r="S5" s="112"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="R3" s="85"/>
+      <c r="S3" s="86"/>
+    </row>
+    <row r="4" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="113" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="104"/>
+      <c r="Q4" s="105"/>
+      <c r="R4" s="106"/>
+      <c r="S4" s="107"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="K5" s="96"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
+      <c r="O5" s="97"/>
+      <c r="P5" s="98"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="101"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="98"/>
-      <c r="L6" s="99"/>
-      <c r="M6" s="99"/>
-      <c r="N6" s="99"/>
-      <c r="O6" s="99"/>
-      <c r="P6" s="100"/>
-      <c r="Q6" s="101"/>
-      <c r="R6" s="102"/>
-      <c r="S6" s="103"/>
-    </row>
-    <row r="7" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="75" t="s">
+      <c r="K6" s="102"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="103"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="106"/>
+      <c r="S6" s="107"/>
+    </row>
+    <row r="7" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="82" t="s">
+      <c r="B7" s="83"/>
+      <c r="C7" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="88" t="s">
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="89"/>
-    </row>
-    <row r="8" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="77" t="str">
-        <f>'API 목록'!C8</f>
-        <v>POST</v>
-      </c>
-      <c r="B8" s="78"/>
-      <c r="C8" s="85" t="str">
-        <f>'API 목록'!B8</f>
-        <v>api/</v>
-      </c>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="90" t="str">
+      <c r="I7" s="109"/>
+    </row>
+    <row r="8" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="89" t="str">
+        <f>'API 목록'!C9</f>
+        <v>GET</v>
+      </c>
+      <c r="B8" s="90"/>
+      <c r="C8" s="91" t="str">
+        <f>'API 목록'!B9</f>
+        <v>https://apis.data.go.kr/1360000/VilageFcstInfoService_2.0</v>
+      </c>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="94" t="str">
         <f>'API 목록'!D8 &amp; ""</f>
         <v>application/json</v>
       </c>
-      <c r="I8" s="91"/>
-    </row>
-    <row r="9" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="I8" s="95"/>
+    </row>
+    <row r="9" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -2443,22 +2466,22 @@
       <c r="G9" s="14"/>
       <c r="I9" s="11"/>
     </row>
-    <row r="11" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="75" t="s">
+    <row r="12" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="76"/>
-      <c r="C12" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="84"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="84" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="86"/>
       <c r="G12" s="12" t="s">
         <v>12</v>
       </c>
@@ -2473,42 +2496,786 @@
       <c r="M12" s="50"/>
       <c r="N12" s="50"/>
     </row>
-    <row r="13" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="73" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="74"/>
+    <row r="13" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="74" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="75"/>
+      <c r="C13" s="74" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="75"/>
       <c r="G13" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="K13" s="50"/>
       <c r="L13" s="50"/>
       <c r="M13" s="50"/>
       <c r="N13" s="50"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.6">
-      <c r="A14" s="104" t="s">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A14" s="77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="78"/>
+      <c r="C14" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A15" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="88"/>
+      <c r="C15" s="74" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="87" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="88"/>
+      <c r="C16" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="76"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A17" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="75"/>
+      <c r="C17" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="74" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="75"/>
+      <c r="C18" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="72" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="73"/>
+      <c r="C19" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20" s="72" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="73"/>
+      <c r="C20" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" s="82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="83"/>
+      <c r="C23" s="84" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="86"/>
+      <c r="G23" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="31.8" x14ac:dyDescent="0.4">
+      <c r="A24" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="75"/>
+      <c r="C24" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="78"/>
+      <c r="C25" s="74" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="H25" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="57"/>
+      <c r="C26" s="74" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H26" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="55"/>
+      <c r="C27" s="74" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H27" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28" s="75"/>
+      <c r="C28" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H28" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29" s="74" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="75"/>
+      <c r="C29" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="76"/>
+      <c r="E29" s="76"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="H29" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A30" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="73"/>
+      <c r="C30" s="74" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="H30" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A31" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" s="73"/>
+      <c r="C31" s="74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="H31" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A32" s="72" t="s">
+        <v>131</v>
+      </c>
+      <c r="B32" s="73"/>
+      <c r="C32" s="74" t="s">
+        <v>133</v>
+      </c>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="H32" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A33" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="73"/>
+      <c r="C33" s="74" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H33" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A34" s="72" t="s">
+        <v>137</v>
+      </c>
+      <c r="B34" s="73"/>
+      <c r="C34" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="H34" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A35" s="72" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="73"/>
+      <c r="C35" s="74" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="H35" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A36" s="72" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="73"/>
+      <c r="C36" s="74" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H36" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A37" s="72" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="73"/>
+      <c r="C37" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H37" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A39" s="130"/>
+      <c r="B39" s="130"/>
+      <c r="C39" s="130"/>
+      <c r="D39" s="130"/>
+      <c r="E39" s="130"/>
+      <c r="F39" s="130"/>
+      <c r="G39" s="130"/>
+      <c r="H39" s="130"/>
+      <c r="I39" s="130"/>
+    </row>
+  </sheetData>
+  <mergeCells count="62">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K3:P3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="K4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="K5:P5"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A29:B29"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:S28"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="6.19921875" customWidth="1"/>
+    <col min="2" max="2" width="13.59765625" customWidth="1"/>
+    <col min="3" max="5" width="2.8984375" customWidth="1"/>
+    <col min="6" max="6" width="9.09765625" customWidth="1"/>
+    <col min="7" max="7" width="44.19921875" customWidth="1"/>
+    <col min="8" max="8" width="9.19921875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="110" t="str">
+        <f>'API 목록'!A8</f>
+        <v>signupf</v>
+      </c>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="112"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="R3" s="85"/>
+      <c r="S3" s="86"/>
+    </row>
+    <row r="4" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="113" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="104"/>
+      <c r="Q4" s="105"/>
+      <c r="R4" s="106"/>
+      <c r="S4" s="107"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="K5" s="96"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
+      <c r="O5" s="97"/>
+      <c r="P5" s="98"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="101"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="102"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="103"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="106"/>
+      <c r="S6" s="107"/>
+    </row>
+    <row r="7" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="82" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="83"/>
+      <c r="C7" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="108" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="109"/>
+    </row>
+    <row r="8" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="89" t="str">
+        <f>'API 목록'!C8</f>
+        <v>POST</v>
+      </c>
+      <c r="B8" s="90"/>
+      <c r="C8" s="91" t="str">
+        <f>'API 목록'!B8</f>
+        <v>api/</v>
+      </c>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="94" t="str">
+        <f>'API 목록'!D8 &amp; ""</f>
+        <v>application/json</v>
+      </c>
+      <c r="I8" s="95"/>
+    </row>
+    <row r="9" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="11" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="83"/>
+      <c r="C12" s="84" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+    </row>
+    <row r="13" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="75"/>
+      <c r="C13" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A14" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="105"/>
-      <c r="C14" s="73" t="s">
+      <c r="B14" s="78"/>
+      <c r="C14" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="106"/>
-      <c r="E14" s="106"/>
-      <c r="F14" s="74"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="75"/>
       <c r="G14" s="16" t="s">
         <v>64</v>
       </c>
@@ -2519,17 +3286,17 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.6">
-      <c r="A15" s="79" t="s">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A15" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="80"/>
-      <c r="C15" s="73" t="s">
+      <c r="B15" s="88"/>
+      <c r="C15" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="106"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="74"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="75"/>
       <c r="G15" s="1" t="s">
         <v>65</v>
       </c>
@@ -2540,51 +3307,51 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.6">
-      <c r="A16" s="79"/>
-      <c r="B16" s="80"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="74"/>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="A16" s="87"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="75"/>
       <c r="G16" s="1"/>
       <c r="H16" s="52"/>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A17" s="73"/>
-      <c r="B17" s="74"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="74"/>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17" s="74"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="75"/>
       <c r="G17" s="5"/>
       <c r="H17" s="24"/>
       <c r="I17" s="15"/>
     </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="73"/>
-      <c r="B18" s="74"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="106"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="74"/>
+    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="74"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="75"/>
       <c r="G18" s="5"/>
       <c r="H18" s="24"/>
       <c r="I18" s="15"/>
     </row>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="94"/>
-      <c r="B19" s="95"/>
-      <c r="C19" s="113"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="115"/>
+    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="72"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="81"/>
       <c r="G19" s="51"/>
       <c r="H19" s="19"/>
       <c r="I19" s="15"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="14"/>
@@ -2593,22 +3360,22 @@
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
     </row>
-    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="75" t="s">
+    <row r="22" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="76"/>
-      <c r="C22" s="82" t="s">
+      <c r="B22" s="83"/>
+      <c r="C22" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="84"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="86"/>
       <c r="G22" s="12" t="s">
         <v>12</v>
       </c>
@@ -2619,17 +3386,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A23" s="96" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" s="116" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="97"/>
-      <c r="C23" s="113" t="s">
+      <c r="B23" s="117"/>
+      <c r="C23" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="114"/>
-      <c r="E23" s="114"/>
-      <c r="F23" s="115"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="81"/>
       <c r="G23" s="16" t="s">
         <v>70</v>
       </c>
@@ -2640,17 +3407,17 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A24" s="92" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" s="114" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="93"/>
-      <c r="C24" s="113" t="s">
+      <c r="B24" s="115"/>
+      <c r="C24" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="114"/>
-      <c r="E24" s="114"/>
-      <c r="F24" s="115"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="81"/>
       <c r="G24" s="1" t="s">
         <v>71</v>
       </c>
@@ -2661,32 +3428,32 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="94"/>
-      <c r="B25" s="95"/>
-      <c r="C25" s="113"/>
-      <c r="D25" s="114"/>
-      <c r="E25" s="114"/>
-      <c r="F25" s="115"/>
+    <row r="25" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="72"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="81"/>
       <c r="G25" s="5"/>
       <c r="H25" s="19"/>
       <c r="I25" s="15"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="I28" s="10" t="s">
         <v>26</v>
       </c>
@@ -2742,141 +3509,403 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="9.8984375" customWidth="1"/>
+    <col min="5" max="5" width="33.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="110" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="112"/>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="118" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="119"/>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="120" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="121"/>
+      <c r="C5" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="122"/>
+      <c r="E5" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="118" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="119"/>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="124"/>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="123" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="124"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="121"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E13" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E13" location="'API 목록'!A1" display="API 목록 가기" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="9.8984375" customWidth="1"/>
+    <col min="5" max="5" width="33.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="112"/>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="118" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="119"/>
+      <c r="C4" s="119" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="119"/>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="120" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="121"/>
+      <c r="C5" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="122"/>
+      <c r="E5" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="118" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="119"/>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="124"/>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="123" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="124"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="120" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="121"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="E13" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E13" location="'API 목록'!A1" display="API 목록 가기" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8200-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.125" customWidth="1"/>
-    <col min="2" max="2" width="7.875" customWidth="1"/>
-    <col min="3" max="3" width="6.625" customWidth="1"/>
-    <col min="4" max="4" width="9.125" customWidth="1"/>
-    <col min="5" max="5" width="39.25" customWidth="1"/>
+    <col min="1" max="1" width="8.09765625" customWidth="1"/>
+    <col min="2" max="2" width="7.8984375" customWidth="1"/>
+    <col min="3" max="3" width="6.59765625" customWidth="1"/>
+    <col min="4" max="4" width="9.09765625" customWidth="1"/>
+    <col min="5" max="5" width="39.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="63" t="s">
+    <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="110" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="65"/>
-    </row>
-    <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="112"/>
+    </row>
+    <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A4" s="66" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67" t="s">
+      <c r="B4" s="119"/>
+      <c r="C4" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="67"/>
+      <c r="D4" s="119"/>
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A5" s="71" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="116" t="s">
+      <c r="B5" s="124"/>
+      <c r="C5" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="116"/>
+      <c r="D5" s="125"/>
       <c r="E5" s="8"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A6" s="117" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="126" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="116" t="s">
+      <c r="B6" s="127"/>
+      <c r="C6" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="116"/>
+      <c r="D6" s="125"/>
       <c r="E6" s="4"/>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A7" s="117" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="116" t="s">
+      <c r="B7" s="127"/>
+      <c r="C7" s="125" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="116"/>
+      <c r="D7" s="125"/>
       <c r="E7" s="8" t="s">
         <v>45</v>
       </c>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A8" s="71" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="116" t="s">
+      <c r="B8" s="124"/>
+      <c r="C8" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="116"/>
+      <c r="D8" s="125"/>
       <c r="E8" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="68" t="s">
+    <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="70" t="s">
+      <c r="B9" s="121"/>
+      <c r="C9" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="70"/>
+      <c r="D9" s="122"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A12" s="66" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67" t="s">
+      <c r="B12" s="119"/>
+      <c r="C12" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="67"/>
+      <c r="D12" s="119"/>
       <c r="E12" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="71" t="s">
+    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="72"/>
+      <c r="B13" s="124"/>
       <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A14" s="71" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="72"/>
+      <c r="B14" s="124"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
         <v>21</v>
@@ -2885,11 +3914,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="68" t="s">
+    <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="69"/>
+      <c r="B15" s="121"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
         <v>24</v>
@@ -2898,7 +3927,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.6">
+    <row r="17" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E17" s="10" t="s">
         <v>26</v>
       </c>
@@ -2932,105 +3961,105 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-8300-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.125" customWidth="1"/>
-    <col min="2" max="2" width="7.875" customWidth="1"/>
-    <col min="3" max="3" width="6.625" customWidth="1"/>
-    <col min="4" max="4" width="9.125" customWidth="1"/>
-    <col min="5" max="5" width="39.25" customWidth="1"/>
+    <col min="1" max="1" width="8.09765625" customWidth="1"/>
+    <col min="2" max="2" width="7.8984375" customWidth="1"/>
+    <col min="3" max="3" width="6.59765625" customWidth="1"/>
+    <col min="4" max="4" width="9.09765625" customWidth="1"/>
+    <col min="5" max="5" width="39.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="63" t="s">
+    <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="110" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="65"/>
-    </row>
-    <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="112"/>
+    </row>
+    <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A4" s="66" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67" t="s">
+      <c r="B4" s="119"/>
+      <c r="C4" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="67"/>
+      <c r="D4" s="119"/>
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A5" s="71" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="116" t="s">
+      <c r="B5" s="124"/>
+      <c r="C5" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="116"/>
+      <c r="D5" s="125"/>
       <c r="E5" s="8"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="119" t="s">
+    <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="128" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="120"/>
-      <c r="C6" s="70" t="s">
+      <c r="B6" s="129"/>
+      <c r="C6" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="70"/>
+      <c r="D6" s="122"/>
       <c r="E6" s="6" t="s">
         <v>52</v>
       </c>
       <c r="F6" s="7"/>
     </row>
-    <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A9" s="66" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="67"/>
-      <c r="C9" s="67" t="s">
+      <c r="B9" s="119"/>
+      <c r="C9" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="67"/>
+      <c r="D9" s="119"/>
       <c r="E9" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="71" t="s">
+    <row r="10" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="72"/>
+      <c r="B10" s="124"/>
       <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="A11" s="71" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="72"/>
+      <c r="B11" s="124"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
         <v>21</v>
@@ -3039,11 +4068,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="68" t="s">
+    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="69"/>
+      <c r="B12" s="121"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5" t="s">
         <v>24</v>
@@ -3052,7 +4081,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="E14" s="10" t="s">
         <v>26</v>
       </c>
